--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484260_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484260_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0354</v>
+        <v>3.1006</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6915</v>
+        <v>4.1652</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6561</v>
+        <v>-1.0646</v>
       </c>
       <c r="G2" t="n">
         <v>-0.2563</v>
@@ -610,13 +610,13 @@
         <v>2.3441</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8489</v>
+        <v>0.9141</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4722</v>
+        <v>0.9459</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3767</v>
+        <v>-0.0318</v>
       </c>
       <c r="V2" t="n">
         <v>1.0754</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1675</v>
+        <v>2.0392</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7844</v>
+        <v>1.411</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3831</v>
+        <v>0.6282</v>
       </c>
       <c r="G3" t="n">
         <v>1.2186</v>
@@ -688,13 +688,13 @@
         <v>1.7581</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8325</v>
+        <v>0.0392</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5034</v>
+        <v>0.1232</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3291</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Q. BARDÉS BADIA</t>
+          <t>S. ESTEVES-GARCIA COFFI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0965</v>
+        <v>1.1762</v>
       </c>
       <c r="E4" t="n">
-        <v>0.157</v>
+        <v>3.4036</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9395</v>
+        <v>-2.2274</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1336</v>
+        <v>-0.1956</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1361</v>
+        <v>0.331</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2696</v>
+        <v>-0.5266</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1433</v>
+        <v>1.6523</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1433</v>
+        <v>1.6385</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.0138</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0097</v>
+        <v>-1.848</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2793</v>
+        <v>-1.3075</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2696</v>
+        <v>-0.5405</v>
       </c>
       <c r="P4" t="n">
-        <v>0.586</v>
+        <v>1.5627</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.586</v>
+        <v>1.5627</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3769</v>
+        <v>0.4519</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0138</v>
+        <v>0.8647</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3631</v>
+        <v>-0.4128</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.6428</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.8865</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.5294</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. ESTEVES-GARCIA COFFI</t>
+          <t>Q. BARDÉS BADIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9263</v>
+        <v>1.0965</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2627</v>
+        <v>0.157</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.3363</v>
+        <v>0.9395</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1956</v>
+        <v>0.1336</v>
       </c>
       <c r="H5" t="n">
-        <v>0.331</v>
+        <v>-0.1361</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5266</v>
+        <v>0.2696</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6523</v>
+        <v>0.1433</v>
       </c>
       <c r="K5" t="n">
-        <v>1.6385</v>
+        <v>0.1433</v>
       </c>
       <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-0.0097</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-0.2793</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.2696</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.3769</v>
+      </c>
+      <c r="T5" t="n">
         <v>0.0138</v>
       </c>
-      <c r="M5" t="n">
-        <v>-1.848</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-1.3075</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-0.5405</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.5627</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.5627</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.202</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.7238</v>
-      </c>
       <c r="U5" t="n">
-        <v>-0.5218</v>
+        <v>0.3631</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6428</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.5294</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.601</v>
+        <v>-0.4061</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.913</v>
+        <v>-0.6908</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3119</v>
+        <v>0.2847</v>
       </c>
       <c r="G6" t="n">
         <v>-1.5788</v>
@@ -922,13 +922,13 @@
         <v>1.1721</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1943</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.652</v>
+        <v>-0.4298</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4577</v>
+        <v>0.4304</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3609</v>
+        <v>-1.0903</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2008</v>
+        <v>-0.0391</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1602</v>
+        <v>-1.0512</v>
       </c>
       <c r="G7" t="n">
         <v>0.4316</v>
@@ -1000,13 +1000,13 @@
         <v>0.1953</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7693</v>
+        <v>-0.4987</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3026</v>
+        <v>-0.141</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4667</v>
+        <v>-0.3577</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2186</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. ROSADO FORNIES</t>
+          <t>J. SOLE PIE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9071</v>
+        <v>-1.5009</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0764</v>
+        <v>-1.4976</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.9835</v>
+        <v>-0.0033</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.4212</v>
+        <v>-2.4257</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.0161</v>
+        <v>-1.7913</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4051</v>
+        <v>-0.6344</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0819</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0819</v>
+        <v>-0.1996</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.503</v>
+        <v>-1.5925</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.098</v>
+        <v>-1.5917</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4051</v>
+        <v>-0.0008</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1953</v>
+        <v>2.3441</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1953</v>
+        <v>2.3441</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3698</v>
+        <v>0.6067</v>
       </c>
       <c r="T8" t="n">
-        <v>1.0456</v>
+        <v>0.3867</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6758</v>
+        <v>0.22</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0511</v>
+        <v>-2.026</v>
       </c>
       <c r="W8" t="n">
         <v>-1.0511</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.9749</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. SOLE PIE</t>
+          <t>A. BARQUETS ARIZA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9936</v>
+        <v>-2.5165</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8814</v>
+        <v>1.1043</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1123</v>
+        <v>-3.6208</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.4257</v>
+        <v>-2.7663</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.7913</v>
+        <v>0.9281</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6344</v>
+        <v>-3.6944</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.8332000000000001</v>
+        <v>-0.2299</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1996</v>
+        <v>2.5198</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-2.7497</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.5925</v>
+        <v>-2.5364</v>
       </c>
       <c r="N9" t="n">
         <v>-1.5917</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0008</v>
+        <v>-0.9447</v>
       </c>
       <c r="P9" t="n">
-        <v>2.3441</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3441</v>
+        <v>1.5627</v>
       </c>
       <c r="S9" t="n">
-        <v>0.114</v>
+        <v>-0.1224</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0029</v>
+        <v>0.6633</v>
       </c>
       <c r="U9" t="n">
-        <v>0.111</v>
+        <v>-0.7857</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.026</v>
+        <v>1.7396</v>
       </c>
       <c r="W9" t="n">
-        <v>-1.0511</v>
+        <v>3.601</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.9749</v>
+        <v>-1.8615</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. BARQUETS ARIZA</t>
+          <t>M. ROSADO FORNIES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.338</v>
+        <v>-2.6071</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9832</v>
+        <v>-0.7326</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.3212</v>
+        <v>-1.8745</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.7663</v>
+        <v>-1.4212</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9281</v>
+        <v>-1.0161</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.6944</v>
+        <v>-0.4051</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2299</v>
+        <v>0.0819</v>
       </c>
       <c r="K10" t="n">
-        <v>2.5198</v>
+        <v>0.0819</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.7497</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.5364</v>
+        <v>-1.503</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.5917</v>
+        <v>-1.098</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9447</v>
+        <v>-0.4051</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.3674</v>
+        <v>0.1953</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5627</v>
+        <v>0.1953</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0561</v>
+        <v>-0.3302</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5422</v>
+        <v>0.2367</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4861</v>
+        <v>-0.5668</v>
       </c>
       <c r="V10" t="n">
-        <v>1.7396</v>
+        <v>-1.0511</v>
       </c>
       <c r="W10" t="n">
-        <v>3.601</v>
+        <v>-1.0511</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.8615</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.4108</v>
+        <v>-6.7376</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.713</v>
+        <v>-3.9853</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.6978</v>
+        <v>-2.7523</v>
       </c>
       <c r="G11" t="n">
         <v>-4.0299</v>
@@ -1312,13 +1312,13 @@
         <v>0.3907</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1754</v>
+        <v>-0.5021</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.0591</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3886</v>
+        <v>-0.4431</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6428</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.9545</v>
+        <v>-7.5828</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.8453</v>
+        <v>-6.5825</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1092</v>
+        <v>-1.0002</v>
       </c>
       <c r="G12" t="n">
         <v>-2.9948</v>
@@ -1390,13 +1390,13 @@
         <v>0.586</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9041</v>
+        <v>-0.5324</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5915</v>
+        <v>-0.3287</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3126</v>
+        <v>-0.2037</v>
       </c>
       <c r="V12" t="n">
         <v>1.2186</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-16.3402</v>
+        <v>-15.0288</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.5983</v>
+        <v>-3.286799999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-11.7421</v>
+        <v>-11.7419</v>
       </c>
       <c r="G13" t="n">
         <v>-13.8848</v>
@@ -1459,7 +1459,7 @@
         <v>-1.3553</v>
       </c>
       <c r="P13" t="n">
-        <v>-9.999999999976694e-05</v>
+        <v>-0.0001000000000015433</v>
       </c>
       <c r="Q13" t="n">
         <v>-12.6972</v>
@@ -1468,13 +1468,13 @@
         <v>12.6971</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9079</v>
+        <v>0.4036</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9642000000000003</v>
+        <v>2.2757</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.8722</v>
+        <v>-1.8721</v>
       </c>
       <c r="V13" t="n">
         <v>-1.5477</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.722099999999999</v>
+        <v>7.2562</v>
       </c>
       <c r="E14" t="n">
-        <v>6.6637</v>
+        <v>4.3381</v>
       </c>
       <c r="F14" t="n">
-        <v>3.0584</v>
+        <v>2.9181</v>
       </c>
       <c r="G14" t="n">
         <v>4.4657</v>
@@ -1546,13 +1546,13 @@
         <v>1.3674</v>
       </c>
       <c r="S14" t="n">
-        <v>4.1903</v>
+        <v>1.7244</v>
       </c>
       <c r="T14" t="n">
-        <v>3.588</v>
+        <v>1.2623</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6022999999999999</v>
+        <v>0.4621</v>
       </c>
       <c r="V14" t="n">
         <v>2.8242</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.2855</v>
+        <v>4.546</v>
       </c>
       <c r="E15" t="n">
-        <v>4.4522</v>
+        <v>4.5533</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1667</v>
+        <v>-0.0073</v>
       </c>
       <c r="G15" t="n">
         <v>3.8865</v>
@@ -1624,13 +1624,13 @@
         <v>1.5627</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4139</v>
+        <v>-0.1534</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1594</v>
+        <v>-0.0583</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2544</v>
+        <v>-0.0951</v>
       </c>
       <c r="V15" t="n">
         <v>-0.5545</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. PRAT PRUNA</t>
+          <t>O. HERAS FLECHA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.693</v>
+        <v>2.695</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3656</v>
+        <v>1.6394</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3274</v>
+        <v>1.0556</v>
       </c>
       <c r="G16" t="n">
-        <v>0.788</v>
+        <v>2.5671</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8936</v>
+        <v>0.3948</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.1056</v>
+        <v>2.1723</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3481</v>
+        <v>2.6614</v>
       </c>
       <c r="K16" t="n">
-        <v>2.397</v>
+        <v>1.4326</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.0489</v>
+        <v>1.2288</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4399</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5034</v>
+        <v>-1.0379</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9433</v>
+        <v>0.9435</v>
       </c>
       <c r="P16" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="Q16" t="n">
         <v>-1.1721</v>
       </c>
-      <c r="Q16" t="n">
-        <v>-2.9301</v>
-      </c>
       <c r="R16" t="n">
-        <v>1.7581</v>
+        <v>1.5627</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6923</v>
+        <v>-0.2628</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0989</v>
+        <v>0.1501</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5933</v>
+        <v>-0.4128</v>
       </c>
       <c r="V16" t="n">
-        <v>2.7693</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>3.0466</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>O. HERAS FLECHA</t>
+          <t>G. PRAT PRUNA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5749</v>
+        <v>2.5448</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0327</v>
+        <v>0.5678</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5422</v>
+        <v>1.977</v>
       </c>
       <c r="G17" t="n">
-        <v>2.5671</v>
+        <v>0.788</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3948</v>
+        <v>1.8936</v>
       </c>
       <c r="I17" t="n">
-        <v>2.1723</v>
+        <v>-1.1056</v>
       </c>
       <c r="J17" t="n">
-        <v>2.6614</v>
+        <v>0.3481</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4326</v>
+        <v>2.397</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2288</v>
+        <v>-2.0489</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.09429999999999999</v>
+        <v>0.4399</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0379</v>
+        <v>-0.5034</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9435</v>
+        <v>0.9433</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3907</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1721</v>
+        <v>-2.9301</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5627</v>
+        <v>1.7581</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3828</v>
+        <v>0.1596</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4566</v>
+        <v>0.1033</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9262</v>
+        <v>0.0562</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>2.7693</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>3.0466</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. HOMS LORENZO</t>
+          <t>A. VIÑALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4924</v>
+        <v>2.1551</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2171</v>
+        <v>1.0072</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2753</v>
+        <v>1.1479</v>
       </c>
       <c r="G18" t="n">
-        <v>1.0004</v>
+        <v>-0.5175999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3507</v>
+        <v>-0.1939</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3504</v>
+        <v>-0.3237</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6951000000000001</v>
+        <v>-0.9577</v>
       </c>
       <c r="K18" t="n">
-        <v>1.989</v>
+        <v>0.3095</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.2939</v>
+        <v>-1.2673</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3053</v>
+        <v>0.4401</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6382</v>
+        <v>-0.5034</v>
       </c>
       <c r="O18" t="n">
         <v>0.9435</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3907</v>
+        <v>1.7581</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9534</v>
+        <v>-0.1953</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5627</v>
+        <v>1.9534</v>
       </c>
       <c r="S18" t="n">
-        <v>1.16</v>
+        <v>0.5826</v>
       </c>
       <c r="T18" t="n">
-        <v>0.589</v>
+        <v>0.3324</v>
       </c>
       <c r="U18" t="n">
-        <v>0.571</v>
+        <v>0.2502</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2772</v>
+        <v>0.3321</v>
       </c>
       <c r="W18" t="n">
-        <v>0.8865</v>
+        <v>1.8279</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.1638</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. SALMERON SEGU</t>
+          <t>A. PEIRO COSMO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.3163</v>
+        <v>1.7477</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5226</v>
+        <v>-0.3057</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2063</v>
+        <v>2.0534</v>
       </c>
       <c r="G19" t="n">
-        <v>2.197</v>
+        <v>-0.1882</v>
       </c>
       <c r="H19" t="n">
-        <v>1.6577</v>
+        <v>-0.4308</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5393</v>
+        <v>0.2426</v>
       </c>
       <c r="J19" t="n">
-        <v>2.3561</v>
+        <v>-0.0988</v>
       </c>
       <c r="K19" t="n">
-        <v>2.3561</v>
+        <v>0.3325</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-0.4313</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1591</v>
+        <v>-0.0895</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6984</v>
+        <v>-0.7634</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5393</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="P19" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="Q19" t="n">
         <v>-0.1953</v>
       </c>
-      <c r="Q19" t="n">
-        <v>-0.9767</v>
-      </c>
       <c r="R19" t="n">
-        <v>0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5332</v>
+        <v>0.2951</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1432</v>
+        <v>-0.0116</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3901</v>
+        <v>0.3067</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2186</v>
+        <v>0.6642</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2186</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. PEIRO COSMO</t>
+          <t>M. SALMERON SEGU</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9712</v>
+        <v>1.5328</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8113</v>
+        <v>1.5226</v>
       </c>
       <c r="F20" t="n">
-        <v>1.7825</v>
+        <v>0.0102</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1882</v>
+        <v>2.197</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4308</v>
+        <v>1.6577</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2426</v>
+        <v>0.5393</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0988</v>
+        <v>2.3561</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3325</v>
+        <v>2.3561</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.4313</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0895</v>
+        <v>-0.1591</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7634</v>
+        <v>-0.6984</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6739000000000001</v>
+        <v>0.5393</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9767</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.1953</v>
+        <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4815</v>
+        <v>0.7498</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5172</v>
+        <v>0.1432</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0357</v>
+        <v>0.6066</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6642</v>
+        <v>-1.2186</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.6642</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. VIÑALLONGA GOMEZ</t>
+          <t>C. HOMS LORENZO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4593</v>
+        <v>1.2149</v>
       </c>
       <c r="E21" t="n">
-        <v>0.09719999999999999</v>
+        <v>-0.0862</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3622</v>
+        <v>1.3011</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.5175999999999999</v>
+        <v>1.0004</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1939</v>
+        <v>1.3507</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3237</v>
+        <v>-0.3504</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9577</v>
+        <v>0.6951000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3095</v>
+        <v>1.989</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.2673</v>
+        <v>-1.2939</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4401</v>
+        <v>0.3053</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5034</v>
+        <v>-0.6382</v>
       </c>
       <c r="O21" t="n">
         <v>0.9435</v>
       </c>
       <c r="P21" t="n">
-        <v>1.7581</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.1953</v>
+        <v>-1.9534</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9534</v>
+        <v>1.5627</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1132</v>
+        <v>0.8825</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5777</v>
+        <v>0.2856</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5355</v>
+        <v>0.5969</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3321</v>
+        <v>-0.2772</v>
       </c>
       <c r="W21" t="n">
-        <v>1.8279</v>
+        <v>0.8865</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.4959</v>
+        <v>-1.1638</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2606</v>
+        <v>0.057</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2553</v>
+        <v>0.3564</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5159</v>
+        <v>-0.2994</v>
       </c>
       <c r="G22" t="n">
         <v>-0.0516</v>
@@ -2170,13 +2170,13 @@
         <v>0.3907</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3224</v>
+        <v>-0.0048</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1073</v>
+        <v>-0.0062</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2152</v>
+        <v>0.0014</v>
       </c>
       <c r="V22" t="n">
         <v>-0.2772</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.9139</v>
+        <v>-4.713</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.0531</v>
+        <v>-1.8509</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.8608</v>
+        <v>-2.8621</v>
       </c>
       <c r="G23" t="n">
         <v>-0.2625</v>
@@ -2248,13 +2248,13 @@
         <v>0.586</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5695</v>
+        <v>-0.3687</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5309</v>
+        <v>-0.3287</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0386</v>
+        <v>-0.04</v>
       </c>
       <c r="V23" t="n">
         <v>-2.7145</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>16.3402</v>
+        <v>19.0365</v>
       </c>
       <c r="E24" t="n">
         <v>11.742</v>
       </c>
       <c r="F24" t="n">
-        <v>4.5983</v>
+        <v>7.294499999999999</v>
       </c>
       <c r="G24" t="n">
         <v>13.8848</v>
@@ -2326,13 +2326,13 @@
         <v>12.6972</v>
       </c>
       <c r="S24" t="n">
-        <v>0.9078999999999998</v>
+        <v>3.6043</v>
       </c>
       <c r="T24" t="n">
-        <v>1.872200000000001</v>
+        <v>1.8721</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.9641000000000002</v>
+        <v>1.7322</v>
       </c>
       <c r="V24" t="n">
         <v>1.5478</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484260_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484260_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,11 +632,16 @@
       <c r="X2" t="n">
         <v>-1.5842</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484260_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. CAMPAÑA SOLER</t>
+          <t>P. CAMPANA SOLER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,28 +653,28 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0392</v>
+        <v>1.7323</v>
       </c>
       <c r="E3" t="n">
-        <v>1.411</v>
+        <v>1.104</v>
       </c>
       <c r="F3" t="n">
         <v>0.6282</v>
       </c>
       <c r="G3" t="n">
-        <v>1.2186</v>
+        <v>0.9117</v>
       </c>
       <c r="H3" t="n">
-        <v>1.583</v>
+        <v>1.276</v>
       </c>
       <c r="I3" t="n">
         <v>-0.3644</v>
       </c>
       <c r="J3" t="n">
-        <v>1.9872</v>
+        <v>1.6803</v>
       </c>
       <c r="K3" t="n">
-        <v>2.6209</v>
+        <v>2.3139</v>
       </c>
       <c r="L3" t="n">
         <v>-0.6336000000000001</v>
@@ -704,6 +714,11 @@
       </c>
       <c r="X3" t="n">
         <v>-0.2772</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484260_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -783,11 +798,16 @@
       <c r="X4" t="n">
         <v>-1.5294</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484260_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Q. BARDÉS BADIA</t>
+          <t>Q. BARDES BADIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -860,12 +880,17 @@
       </c>
       <c r="X5" t="n">
         <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484260_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. SEGARRA BAQUES</t>
+          <t>P. CAMPAÑA SOLER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +902,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4061</v>
+        <v>0.307</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6908</v>
+        <v>0.307</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2847</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.5788</v>
+        <v>0.307</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.1737</v>
+        <v>0.307</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4051</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.261</v>
+        <v>0.307</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4131</v>
+        <v>0.307</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6741</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.3178</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.5868</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.269</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4298</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4304</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -938,12 +963,17 @@
       </c>
       <c r="X6" t="n">
         <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484260_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X. ALMIRALL CANALS</t>
+          <t>M. SEGARRA BAQUES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0903</v>
+        <v>-0.4061</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0391</v>
+        <v>-0.6908</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0512</v>
+        <v>0.2847</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4316</v>
+        <v>-1.5788</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1215</v>
+        <v>-1.1737</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3101</v>
+        <v>-0.4051</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1019</v>
+        <v>-0.261</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0614</v>
+        <v>0.4131</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0405</v>
+        <v>-0.6741</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3298</v>
+        <v>-1.3178</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0601</v>
+        <v>-1.5868</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2696</v>
+        <v>0.269</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4987</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.141</v>
+        <v>-0.4298</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3577</v>
+        <v>0.4304</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484260_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. SOLE PIE</t>
+          <t>X. ALMIRALL CANALS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5009</v>
+        <v>-1.0903</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4976</v>
+        <v>-0.0391</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0033</v>
+        <v>-1.0512</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.4257</v>
+        <v>0.4316</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.7913</v>
+        <v>0.1215</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6344</v>
+        <v>0.3101</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.8332000000000001</v>
+        <v>0.1019</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1996</v>
+        <v>0.0614</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0.0405</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5925</v>
+        <v>0.3298</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.5917</v>
+        <v>0.0601</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0008</v>
+        <v>0.2696</v>
       </c>
       <c r="P8" t="n">
-        <v>2.3441</v>
+        <v>0.1953</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3441</v>
+        <v>0.1953</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6067</v>
+        <v>-0.4987</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3867</v>
+        <v>-0.141</v>
       </c>
       <c r="U8" t="n">
-        <v>0.22</v>
+        <v>-0.3577</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.026</v>
+        <v>-1.2186</v>
       </c>
       <c r="W8" t="n">
-        <v>-1.0511</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.9749</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484260_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. BARQUETS ARIZA</t>
+          <t>J. SOLE PIE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.5165</v>
+        <v>-1.5009</v>
       </c>
       <c r="E9" t="n">
-        <v>1.1043</v>
+        <v>-1.4976</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.6208</v>
+        <v>-0.0033</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.7663</v>
+        <v>-2.4257</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9281</v>
+        <v>-1.7913</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.6944</v>
+        <v>-0.6344</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2299</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>2.5198</v>
+        <v>-0.1996</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.7497</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.5364</v>
+        <v>-1.5925</v>
       </c>
       <c r="N9" t="n">
         <v>-1.5917</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9447</v>
+        <v>-0.0008</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.3674</v>
+        <v>2.3441</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5627</v>
+        <v>2.3441</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1224</v>
+        <v>0.6067</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6633</v>
+        <v>0.3867</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7857</v>
+        <v>0.22</v>
       </c>
       <c r="V9" t="n">
-        <v>1.7396</v>
+        <v>-2.026</v>
       </c>
       <c r="W9" t="n">
-        <v>3.601</v>
+        <v>-1.0511</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.8615</v>
+        <v>-0.9749</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484260_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. ROSADO FORNIES</t>
+          <t>A. BARQUETS ARIZA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6071</v>
+        <v>-2.5165</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7326</v>
+        <v>1.1043</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8745</v>
+        <v>-3.6208</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.4212</v>
+        <v>-2.7663</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.0161</v>
+        <v>0.9281</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4051</v>
+        <v>-3.6944</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0819</v>
+        <v>-0.2299</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0819</v>
+        <v>2.5198</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-2.7497</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.503</v>
+        <v>-2.5364</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.098</v>
+        <v>-1.5917</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4051</v>
+        <v>-0.9447</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1953</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1953</v>
+        <v>1.5627</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3302</v>
+        <v>-0.1224</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2367</v>
+        <v>0.6633</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5668</v>
+        <v>-0.7857</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0511</v>
+        <v>1.7396</v>
       </c>
       <c r="W10" t="n">
-        <v>-1.0511</v>
+        <v>3.601</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.8615</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484260_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. ROY CARNICER</t>
+          <t>M. ROSADO FORNIES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.7376</v>
+        <v>-2.6071</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.9853</v>
+        <v>-0.7326</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.7523</v>
+        <v>-1.8745</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.0299</v>
+        <v>-1.4212</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.6657</v>
+        <v>-1.0161</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3642</v>
+        <v>-0.4051</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.9728</v>
+        <v>0.0819</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.879</v>
+        <v>0.0819</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.09379999999999999</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.0571</v>
+        <v>-1.503</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.7866</v>
+        <v>-1.098</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2704</v>
+        <v>-0.4051</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.5627</v>
+        <v>0.1953</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5021</v>
+        <v>-0.3302</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0591</v>
+        <v>0.2367</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4431</v>
+        <v>-0.5668</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6428</v>
+        <v>-1.0511</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-1.0511</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.6428</v>
+        <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484260_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. MARTIN TRENADO</t>
+          <t>D. ROY CARNICER</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1400,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.5828</v>
+        <v>-6.7376</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.5825</v>
+        <v>-3.9853</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0002</v>
+        <v>-2.7523</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.9948</v>
+        <v>-4.0299</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.6866</v>
+        <v>-3.6657</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.3081</v>
+        <v>-0.3642</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.6122</v>
+        <v>-1.9728</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3044</v>
+        <v>-1.879</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.3077</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.3826</v>
+        <v>-2.0571</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.3822</v>
+        <v>-1.7866</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.0004</v>
+        <v>-0.2704</v>
       </c>
       <c r="P12" t="n">
-        <v>-5.2743</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q12" t="n">
-        <v>-5.8603</v>
+        <v>-1.9534</v>
       </c>
       <c r="R12" t="n">
-        <v>0.586</v>
+        <v>0.3907</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5324</v>
+        <v>-0.5021</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3287</v>
+        <v>-0.0591</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2037</v>
+        <v>-0.4431</v>
       </c>
       <c r="V12" t="n">
-        <v>1.2186</v>
+        <v>-0.6428</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0.6428</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484260_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>J. MARTIN TRENADO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,151 +1483,157 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-15.0288</v>
+        <v>-7.5828</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.286799999999999</v>
+        <v>-6.5825</v>
       </c>
       <c r="F13" t="n">
-        <v>-11.7419</v>
+        <v>-1.0002</v>
       </c>
       <c r="G13" t="n">
-        <v>-13.8848</v>
+        <v>-2.9948</v>
       </c>
       <c r="H13" t="n">
-        <v>-5.7906</v>
+        <v>-1.6866</v>
       </c>
       <c r="I13" t="n">
-        <v>-8.094200000000001</v>
+        <v>-1.3081</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5939000000000001</v>
+        <v>-1.6122</v>
       </c>
       <c r="K13" t="n">
-        <v>7.332999999999999</v>
+        <v>-0.3044</v>
       </c>
       <c r="L13" t="n">
-        <v>-6.738899999999999</v>
+        <v>-1.3077</v>
       </c>
       <c r="M13" t="n">
-        <v>-14.4786</v>
+        <v>-1.3826</v>
       </c>
       <c r="N13" t="n">
-        <v>-13.1235</v>
+        <v>-1.3822</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.3553</v>
+        <v>-0.0004</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.0001000000000015433</v>
+        <v>-5.2743</v>
       </c>
       <c r="Q13" t="n">
-        <v>-12.6972</v>
+        <v>-5.8603</v>
       </c>
       <c r="R13" t="n">
-        <v>12.6971</v>
+        <v>0.586</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4036</v>
+        <v>-0.5324</v>
       </c>
       <c r="T13" t="n">
-        <v>2.2757</v>
+        <v>-0.3287</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.8721</v>
+        <v>-0.2037</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.5477</v>
+        <v>1.2186</v>
       </c>
       <c r="W13" t="n">
-        <v>6.540700000000001</v>
+        <v>1.2186</v>
       </c>
       <c r="X13" t="n">
-        <v>-8.0886</v>
+        <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484260_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>O. TOURE JABBY</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>C.B. GRANOLLERS</t>
+          <t>TENEA-C.B. ESPARREGUERA</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.2562</v>
+        <v>-15.0287</v>
       </c>
       <c r="E14" t="n">
-        <v>4.3381</v>
+        <v>-3.286800000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>2.9181</v>
+        <v>-11.7419</v>
       </c>
       <c r="G14" t="n">
-        <v>4.4657</v>
+        <v>-13.8847</v>
       </c>
       <c r="H14" t="n">
-        <v>3.549</v>
+        <v>-5.7906</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9167</v>
+        <v>-8.094200000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>4.1509</v>
+        <v>0.5939999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>3.5034</v>
+        <v>7.332999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6475</v>
+        <v>-6.738899999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3148</v>
+        <v>-14.4786</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0456</v>
+        <v>-13.1235</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2692</v>
+        <v>-1.3553</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.7581</v>
+        <v>-9.999999999976694e-05</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.1255</v>
+        <v>-12.6972</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3674</v>
+        <v>12.6971</v>
       </c>
       <c r="S14" t="n">
-        <v>1.7244</v>
+        <v>0.4036</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2623</v>
+        <v>2.2757</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4621</v>
+        <v>-1.8721</v>
       </c>
       <c r="V14" t="n">
-        <v>2.8242</v>
+        <v>-1.5477</v>
       </c>
       <c r="W14" t="n">
-        <v>2.0503</v>
+        <v>6.540700000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7739</v>
-      </c>
+        <v>-8.0886</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. MURCIANO PUJADAS</t>
+          <t>O. TOURE JABBY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.546</v>
+        <v>7.2562</v>
       </c>
       <c r="E15" t="n">
-        <v>4.5533</v>
+        <v>4.3381</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0073</v>
+        <v>2.9181</v>
       </c>
       <c r="G15" t="n">
-        <v>3.8865</v>
+        <v>4.4657</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.2645</v>
+        <v>3.549</v>
       </c>
       <c r="I15" t="n">
-        <v>6.151</v>
+        <v>0.9167</v>
       </c>
       <c r="J15" t="n">
-        <v>4.5298</v>
+        <v>4.1509</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.408</v>
+        <v>3.5034</v>
       </c>
       <c r="L15" t="n">
-        <v>4.9378</v>
+        <v>0.6475</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.6433</v>
+        <v>0.3148</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.8565</v>
+        <v>0.0456</v>
       </c>
       <c r="O15" t="n">
-        <v>1.2132</v>
+        <v>0.2692</v>
       </c>
       <c r="P15" t="n">
+        <v>-1.7581</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-3.1255</v>
+      </c>
+      <c r="R15" t="n">
         <v>1.3674</v>
       </c>
-      <c r="Q15" t="n">
-        <v>-0.1953</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.5627</v>
-      </c>
       <c r="S15" t="n">
-        <v>-0.1534</v>
+        <v>1.7244</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0583</v>
+        <v>1.2623</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0951</v>
+        <v>0.4621</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.5545</v>
+        <v>2.8242</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2772</v>
+        <v>2.0503</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.8317</v>
+        <v>0.7739</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484260_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O. HERAS FLECHA</t>
+          <t>A. MURCIANO PUJADAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.695</v>
+        <v>4.546</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6394</v>
+        <v>4.5533</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0556</v>
+        <v>-0.0073</v>
       </c>
       <c r="G16" t="n">
-        <v>2.5671</v>
+        <v>3.8865</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3948</v>
+        <v>-2.2645</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1723</v>
+        <v>6.151</v>
       </c>
       <c r="J16" t="n">
-        <v>2.6614</v>
+        <v>4.5298</v>
       </c>
       <c r="K16" t="n">
-        <v>1.4326</v>
+        <v>-0.408</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2288</v>
+        <v>4.9378</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.09429999999999999</v>
+        <v>-0.6433</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.0379</v>
+        <v>-1.8565</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9435</v>
+        <v>1.2132</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3907</v>
+        <v>1.3674</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1721</v>
+        <v>-0.1953</v>
       </c>
       <c r="R16" t="n">
         <v>1.5627</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2628</v>
+        <v>-0.1534</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1501</v>
+        <v>-0.0583</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4128</v>
+        <v>-0.0951</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.5545</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.8317</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484260_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. PRAT PRUNA</t>
+          <t>O. HERAS FLECHA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.5448</v>
+        <v>2.695</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5678</v>
+        <v>1.6394</v>
       </c>
       <c r="F17" t="n">
-        <v>1.977</v>
+        <v>1.0556</v>
       </c>
       <c r="G17" t="n">
-        <v>0.788</v>
+        <v>2.5671</v>
       </c>
       <c r="H17" t="n">
-        <v>1.8936</v>
+        <v>0.3948</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.1056</v>
+        <v>2.1723</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3481</v>
+        <v>2.6614</v>
       </c>
       <c r="K17" t="n">
-        <v>2.397</v>
+        <v>1.4326</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.0489</v>
+        <v>1.2288</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4399</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5034</v>
+        <v>-1.0379</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9433</v>
+        <v>0.9435</v>
       </c>
       <c r="P17" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="Q17" t="n">
         <v>-1.1721</v>
       </c>
-      <c r="Q17" t="n">
-        <v>-2.9301</v>
-      </c>
       <c r="R17" t="n">
-        <v>1.7581</v>
+        <v>1.5627</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1596</v>
+        <v>-0.2628</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1033</v>
+        <v>0.1501</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0562</v>
+        <v>-0.4128</v>
       </c>
       <c r="V17" t="n">
-        <v>2.7693</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>3.0466</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484260_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. VIÑALLONGA GOMEZ</t>
+          <t>G. PRAT PRUNA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1894,72 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.1551</v>
+        <v>2.5448</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0072</v>
+        <v>0.5678</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1479</v>
+        <v>1.977</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5175999999999999</v>
+        <v>0.788</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1939</v>
+        <v>1.8936</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3237</v>
+        <v>-1.1056</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.9577</v>
+        <v>0.3481</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3095</v>
+        <v>2.397</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.2673</v>
+        <v>-2.0489</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4401</v>
+        <v>0.4399</v>
       </c>
       <c r="N18" t="n">
         <v>-0.5034</v>
       </c>
       <c r="O18" t="n">
-        <v>0.9435</v>
+        <v>0.9433</v>
       </c>
       <c r="P18" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R18" t="n">
         <v>1.7581</v>
       </c>
-      <c r="Q18" t="n">
-        <v>-0.1953</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.9534</v>
-      </c>
       <c r="S18" t="n">
-        <v>0.5826</v>
+        <v>0.1596</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3324</v>
+        <v>0.1033</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2502</v>
+        <v>0.0562</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3321</v>
+        <v>2.7693</v>
       </c>
       <c r="W18" t="n">
-        <v>1.8279</v>
+        <v>3.0466</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.4959</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484260_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0.6642</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484260_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,11 +2122,16 @@
       <c r="X20" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484260_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C. HOMS LORENZO</t>
+          <t>A. VIÑALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.2149</v>
+        <v>1.2279</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0862</v>
+        <v>1.2279</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3011</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>1.0004</v>
+        <v>1.2279</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3507</v>
+        <v>1.2279</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3504</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6951000000000001</v>
+        <v>1.2279</v>
       </c>
       <c r="K21" t="n">
-        <v>1.989</v>
+        <v>1.2279</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.2939</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3053</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6382</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>0.9435</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8825</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5969</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.1638</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484260_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. MASPONS MOLINS</t>
+          <t>C. HOMS LORENZO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.057</v>
+        <v>1.2149</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3564</v>
+        <v>-0.0862</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2994</v>
+        <v>1.3011</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.0516</v>
+        <v>1.0004</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1059</v>
+        <v>1.3507</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0543</v>
+        <v>-0.3504</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3625</v>
+        <v>0.6951000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3083</v>
+        <v>1.989</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0543</v>
+        <v>-1.2939</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4142</v>
+        <v>0.3053</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4142</v>
+        <v>-0.6382</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>0.9435</v>
       </c>
       <c r="P22" t="n">
-        <v>0.3907</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3907</v>
+        <v>1.5627</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0048</v>
+        <v>0.8825</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0062</v>
+        <v>0.2856</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0014</v>
+        <v>0.5969</v>
       </c>
       <c r="V22" t="n">
         <v>-0.2772</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.8865</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2772</v>
+        <v>-1.1638</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484260_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. JUAREZ GIMENEZ</t>
+          <t>A. VINALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.713</v>
+        <v>0.9272</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8509</v>
+        <v>-0.2207</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.8621</v>
+        <v>1.1479</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.2625</v>
+        <v>-1.7456</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0601</v>
+        <v>-1.4218</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2023</v>
+        <v>-0.3237</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4313</v>
+        <v>-2.1857</v>
       </c>
       <c r="K23" t="n">
-        <v>0.903</v>
+        <v>-0.9184</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.4718</v>
+        <v>-1.2673</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.6937</v>
+        <v>0.4401</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.9631999999999999</v>
+        <v>-0.5034</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2694</v>
+        <v>0.9435</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.3674</v>
+        <v>1.7581</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9534</v>
+        <v>-0.1953</v>
       </c>
       <c r="R23" t="n">
-        <v>0.586</v>
+        <v>1.9534</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3687</v>
+        <v>0.5826</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3287</v>
+        <v>0.3324</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.04</v>
+        <v>0.2502</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.7145</v>
+        <v>0.3321</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.8279</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.7145</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484260_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>I. MASPONS MOLINS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,68 +2392,235 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>19.0365</v>
+        <v>0.057</v>
       </c>
       <c r="E24" t="n">
+        <v>0.3564</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-0.2994</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-0.0516</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.1059</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.0543</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.3083</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.0543</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-0.4142</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.4142</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-0.0048</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.0062</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484260_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>J. JUAREZ GIMENEZ</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>C.B. GRANOLLERS</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-4.713</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-1.8509</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-2.8621</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-0.2625</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.0601</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.2023</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.4313</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-0.4718</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-0.6937</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.9631999999999999</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.2694</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-1.3674</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.3687</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.3287</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-2.7145</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-2.7145</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484260_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>C.B. GRANOLLERS</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>19.03649999999999</v>
+      </c>
+      <c r="E26" t="n">
         <v>11.742</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F26" t="n">
         <v>7.294499999999999</v>
       </c>
-      <c r="G24" t="n">
-        <v>13.8848</v>
-      </c>
-      <c r="H24" t="n">
-        <v>5.7906</v>
-      </c>
-      <c r="I24" t="n">
+      <c r="G26" t="n">
+        <v>13.8847</v>
+      </c>
+      <c r="H26" t="n">
+        <v>5.790599999999999</v>
+      </c>
+      <c r="I26" t="n">
         <v>8.094199999999999</v>
       </c>
-      <c r="J24" t="n">
-        <v>14.4787</v>
-      </c>
-      <c r="K24" t="n">
+      <c r="J26" t="n">
+        <v>14.4786</v>
+      </c>
+      <c r="K26" t="n">
         <v>13.1234</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L26" t="n">
         <v>1.3552</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M26" t="n">
         <v>-0.594</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N26" t="n">
         <v>-7.332999999999999</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O26" t="n">
         <v>6.7388</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P26" t="n">
         <v>2.220446049250313e-16</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q26" t="n">
         <v>-12.6971</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R26" t="n">
         <v>12.6972</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S26" t="n">
         <v>3.6043</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T26" t="n">
         <v>1.8721</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U26" t="n">
         <v>1.7322</v>
       </c>
-      <c r="V24" t="n">
+      <c r="V26" t="n">
         <v>1.5478</v>
       </c>
-      <c r="W24" t="n">
+      <c r="W26" t="n">
         <v>8.0885</v>
       </c>
-      <c r="X24" t="n">
-        <v>-6.5408</v>
-      </c>
+      <c r="X26" t="n">
+        <v>-6.540800000000001</v>
+      </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
